--- a/inspection_forms/048_spare_wheel_inspection_checklist--inspection_forms.xlsx
+++ b/inspection_forms/048_spare_wheel_inspection_checklist--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,30 +515,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>inspection_form_1</t>
+          <t>wheel_type</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>inspection_form_1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What type of spare wheel is this?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please select the type of spare wheel.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,13 +552,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>wheel_condition</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is the condition of this wheel?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please select the condition.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +579,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>wheel_pressure</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What is the wheel pressure?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please enter the pressure in PSI.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,61 +601,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>wheel_tread_depth</t>
+          <t>tire_tread_depth</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>wheel_tread_depth</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What is the tire tread depth?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please enter the depth in mm.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>wheel_center_capsules</t>
+          <t>vehicle_model_year</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>wheel_center_capsules</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What is the vehicle model year?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please enter the year.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>wheel_rim_condition</t>
+          <t>vehicle_registration_number</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wheel_rim_condition</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What is the vehicle registration number?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please enter the registration number.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>tire_pressure</t>
+          <t>vehicle_color</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>tire_pressure</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is the vehicle color?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please select the color.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,23 +704,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>tire_tread_depth</t>
+          <t>tire_type</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>tire_tread_depth</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What type of tire is this?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please select the type.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,64 +736,76 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>vehicle_condition</t>
+          <t>spare_wheel_type</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>vehicle_condition</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Spare Wheel Type</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please select the type.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>vehicle_model_year</t>
+          <t>spare_wheel_condition</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>vehicle_model_year</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What is the condition of this spare wheel?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please select the condition.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>vehicle_model_year</t>
+          <t>inspection_date</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>vehicle_model_year</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What is the inspection date?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please enter the inspection date.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +817,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>vehicle_model_year</t>
+          <t>inspector_name</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>vehicle_model_year</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What is the inspector's name?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please enter the name.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,38 +844,46 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>vehicle_model_year</t>
+          <t>inspector_signature</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>vehicle_model_year</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Inspector's signature?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please sign.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>vehicle_registration_number</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>vehicle_registration_number</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Additional notes?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please enter any additional notes.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -842,15 +898,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>vehicle_make</t>
+          <t>vehicle_model</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>vehicle_make</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>What is the vehicle model?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please enter the model.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -870,10 +930,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>vehicle_year</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>What is the vehicle year?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please enter the year.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -883,20 +947,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>vehicle_model</t>
+          <t>spare_wheel_rim_condition</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>vehicle_model</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>What is the condition of this spare wheel's rim?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please select the condition.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -906,182 +974,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>vehicle_color</t>
+          <t>vehicle_status</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>vehicle_color</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>What is the vehicle status?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please select the status.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>tire_type</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>tire_type</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>spare_wheel_type</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>spare_wheel_type</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>spare_wheel_condition</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>spare_wheel_condition</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>inspection_date</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>inspection_date</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>inspector_name</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>inspector_name</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>inspector_signature</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>inspector_signature</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +1009,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,357 +1037,408 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>wheel_condition_choices</t>
+          <t>wheel_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'new'}</t>
+          <t>pneumatic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'New'}</t>
+          <t>Pneumatic</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>wheel_condition_choices</t>
+          <t>wheel_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'used'}</t>
+          <t>semi_pneumatic</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Used'}</t>
+          <t>Semi Pneumatic</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>wheel_condition_choices</t>
+          <t>wheel_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'worn'}</t>
+          <t>non_pneumatic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Worn'}</t>
+          <t>Non Pneumatic</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>wheel_center_capsules_choices</t>
+          <t>wheel_condition_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>wheel_center_capsules_choices</t>
+          <t>wheel_condition_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'used'}</t>
+          <t>used</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Used'}</t>
+          <t>Used</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>wheel_center_capsules_choices</t>
+          <t>wheel_condition_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'worn'}</t>
+          <t>worn</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Worn'}</t>
+          <t>Worn</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>wheel_rim_condition_choices</t>
+          <t>vehicle_color_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'new'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'New'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>wheel_rim_condition_choices</t>
+          <t>vehicle_color_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'used'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Used'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>wheel_rim_condition_choices</t>
+          <t>vehicle_color_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'worn'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Worn'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>vehicle_condition_choices</t>
+          <t>tire_type_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'new'}</t>
+          <t>pneumatic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'New'}</t>
+          <t>Pneumatic</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>vehicle_condition_choices</t>
+          <t>tire_type_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'used'}</t>
+          <t>semi_pneumatic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Used'}</t>
+          <t>Semi Pneumatic</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>vehicle_condition_choices</t>
+          <t>tire_type_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'worn'}</t>
+          <t>non_pneumatic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Worn'}</t>
+          <t>Non Pneumatic</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tire_type_choices</t>
+          <t>spare_wheel_type_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pneumatic'}</t>
+          <t>pneumatic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Pneumatic'}</t>
+          <t>Pneumatic</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tire_type_choices</t>
+          <t>spare_wheel_type_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'semi_pneumatic'}</t>
+          <t>semi_pneumatic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Semi Pneumatic'}</t>
+          <t>Semi Pneumatic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tire_type_choices</t>
+          <t>spare_wheel_type_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'non_pneumatic'}</t>
+          <t>non_pneumatic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Non Pneumatic'}</t>
+          <t>Non Pneumatic</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>spare_wheel_type_choices</t>
+          <t>spare_wheel_condition_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pneumatic'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Pneumatic'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>spare_wheel_type_choices</t>
+          <t>spare_wheel_condition_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'semi_pneumatic'}</t>
+          <t>used</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Semi Pneumatic'}</t>
+          <t>Used</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>spare_wheel_type_choices</t>
+          <t>spare_wheel_condition_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'non_pneumatic'}</t>
+          <t>worn</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Non Pneumatic'}</t>
+          <t>Worn</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>spare_wheel_condition_choices</t>
+          <t>spare_wheel_rim_condition_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>spare_wheel_condition_choices</t>
+          <t>spare_wheel_rim_condition_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'used'}</t>
+          <t>used</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Used'}</t>
+          <t>Used</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>spare_wheel_condition_choices</t>
+          <t>spare_wheel_rim_condition_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'worn'}</t>
+          <t>worn</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Worn'}</t>
+          <t>Worn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>vehicle_status_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>vehicle_status_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>used</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Used</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>vehicle_status_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>worn</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Worn</t>
         </is>
       </c>
     </row>
